--- a/DBs/nfl/Results/NFL_2016_Results.xlsx
+++ b/DBs/nfl/Results/NFL_2016_Results.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tjsut\TracerProjects2\NFL_Elo\Results\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tjsut\tracersports-app\DBs\nfl\Results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B74D72F9-B6DE-418C-B370-036C217EF499}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6DE8D5E-59EA-4C07-8335-D36578CEB2AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{B25168B7-4438-49F2-8A98-7AD70982D7DA}"/>
   </bookViews>
@@ -157,9 +157,6 @@
     <t>SF</t>
   </si>
   <si>
-    <t>STL</t>
-  </si>
-  <si>
     <t>P</t>
   </si>
   <si>
@@ -176,6 +173,9 @@
   </si>
   <si>
     <t>N</t>
+  </si>
+  <si>
+    <t>LAR</t>
   </si>
 </sst>
 </file>
@@ -2032,7 +2032,7 @@
         <v>44</v>
       </c>
       <c r="F32" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="G32" t="s">
         <v>14</v>
@@ -2061,7 +2061,7 @@
         <v>11</v>
       </c>
       <c r="E33" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="F33" t="s">
         <v>44</v>
@@ -2733,7 +2733,7 @@
         <v>11</v>
       </c>
       <c r="E54" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="F54" t="s">
         <v>34</v>
@@ -2768,7 +2768,7 @@
         <v>34</v>
       </c>
       <c r="F55" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="G55" t="s">
         <v>15</v>
@@ -3693,7 +3693,7 @@
         <v>11</v>
       </c>
       <c r="E84" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="F84" t="s">
         <v>20</v>
@@ -3728,7 +3728,7 @@
         <v>20</v>
       </c>
       <c r="F85" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="G85" t="s">
         <v>14</v>
@@ -4781,7 +4781,7 @@
         <v>11</v>
       </c>
       <c r="E118" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="F118" t="s">
         <v>41</v>
@@ -4816,7 +4816,7 @@
         <v>41</v>
       </c>
       <c r="F119" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="G119" t="s">
         <v>14</v>
@@ -5680,7 +5680,7 @@
         <v>17</v>
       </c>
       <c r="F146" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="G146" t="s">
         <v>15</v>
@@ -5709,7 +5709,7 @@
         <v>11</v>
       </c>
       <c r="E147" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="F147" t="s">
         <v>17</v>
@@ -6320,7 +6320,7 @@
         <v>36</v>
       </c>
       <c r="F166" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="G166" t="s">
         <v>14</v>
@@ -6349,7 +6349,7 @@
         <v>11</v>
       </c>
       <c r="E167" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="F167" t="s">
         <v>36</v>
@@ -7024,7 +7024,7 @@
         <v>38</v>
       </c>
       <c r="F188" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="G188" t="s">
         <v>15</v>
@@ -7053,7 +7053,7 @@
         <v>11</v>
       </c>
       <c r="E189" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="F189" t="s">
         <v>38</v>
@@ -9200,7 +9200,7 @@
         <v>13</v>
       </c>
       <c r="F256" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="G256" t="s">
         <v>15</v>
@@ -9229,7 +9229,7 @@
         <v>11</v>
       </c>
       <c r="E257" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="F257" t="s">
         <v>13</v>
@@ -10093,7 +10093,7 @@
         <v>11</v>
       </c>
       <c r="E284" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="F284" t="s">
         <v>25</v>
@@ -10128,7 +10128,7 @@
         <v>25</v>
       </c>
       <c r="F285" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="G285" t="s">
         <v>14</v>
@@ -11056,7 +11056,7 @@
         <v>35</v>
       </c>
       <c r="F314" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="G314" t="s">
         <v>15</v>
@@ -11085,7 +11085,7 @@
         <v>11</v>
       </c>
       <c r="E315" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="F315" t="s">
         <v>35</v>
@@ -11952,7 +11952,7 @@
         <v>33</v>
       </c>
       <c r="F342" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="G342" t="s">
         <v>14</v>
@@ -11981,7 +11981,7 @@
         <v>11</v>
       </c>
       <c r="E343" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="F343" t="s">
         <v>33</v>
@@ -12912,7 +12912,7 @@
         <v>40</v>
       </c>
       <c r="F372" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="G372" t="s">
         <v>14</v>
@@ -12941,7 +12941,7 @@
         <v>11</v>
       </c>
       <c r="E373" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="F373" t="s">
         <v>40</v>
@@ -14064,7 +14064,7 @@
         <v>21</v>
       </c>
       <c r="F408" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="G408" t="s">
         <v>15</v>
@@ -14093,7 +14093,7 @@
         <v>11</v>
       </c>
       <c r="E409" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="F409" t="s">
         <v>21</v>
@@ -14384,7 +14384,7 @@
         <v>34</v>
       </c>
       <c r="F418" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="G418" t="s">
         <v>14</v>
@@ -14413,7 +14413,7 @@
         <v>11</v>
       </c>
       <c r="E419" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="F419" t="s">
         <v>34</v>
@@ -16112,7 +16112,7 @@
         <v>44</v>
       </c>
       <c r="F472" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="G472" t="s">
         <v>15</v>
@@ -16141,7 +16141,7 @@
         <v>11</v>
       </c>
       <c r="E473" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="F473" t="s">
         <v>44</v>
@@ -17072,7 +17072,7 @@
         <v>41</v>
       </c>
       <c r="F502" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="G502" t="s">
         <v>15</v>
@@ -17101,7 +17101,7 @@
         <v>11</v>
       </c>
       <c r="E503" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="F503" t="s">
         <v>41</v>
@@ -17447,10 +17447,10 @@
         <v>2016</v>
       </c>
       <c r="C514" t="s">
+        <v>45</v>
+      </c>
+      <c r="D514" t="s">
         <v>46</v>
-      </c>
-      <c r="D514" t="s">
-        <v>47</v>
       </c>
       <c r="E514" t="s">
         <v>22</v>
@@ -17479,10 +17479,10 @@
         <v>2016</v>
       </c>
       <c r="C515" t="s">
+        <v>45</v>
+      </c>
+      <c r="D515" t="s">
         <v>46</v>
-      </c>
-      <c r="D515" t="s">
-        <v>47</v>
       </c>
       <c r="E515" t="s">
         <v>32</v>
@@ -17511,10 +17511,10 @@
         <v>2016</v>
       </c>
       <c r="C516" t="s">
+        <v>45</v>
+      </c>
+      <c r="D516" t="s">
         <v>46</v>
-      </c>
-      <c r="D516" t="s">
-        <v>47</v>
       </c>
       <c r="E516" t="s">
         <v>34</v>
@@ -17543,10 +17543,10 @@
         <v>2016</v>
       </c>
       <c r="C517" t="s">
+        <v>45</v>
+      </c>
+      <c r="D517" t="s">
         <v>46</v>
-      </c>
-      <c r="D517" t="s">
-        <v>47</v>
       </c>
       <c r="E517" t="s">
         <v>36</v>
@@ -17575,10 +17575,10 @@
         <v>2016</v>
       </c>
       <c r="C518" t="s">
+        <v>45</v>
+      </c>
+      <c r="D518" t="s">
         <v>46</v>
-      </c>
-      <c r="D518" t="s">
-        <v>47</v>
       </c>
       <c r="E518" t="s">
         <v>42</v>
@@ -17607,10 +17607,10 @@
         <v>2016</v>
       </c>
       <c r="C519" t="s">
+        <v>45</v>
+      </c>
+      <c r="D519" t="s">
         <v>46</v>
-      </c>
-      <c r="D519" t="s">
-        <v>47</v>
       </c>
       <c r="E519" t="s">
         <v>35</v>
@@ -17639,10 +17639,10 @@
         <v>2016</v>
       </c>
       <c r="C520" t="s">
+        <v>45</v>
+      </c>
+      <c r="D520" t="s">
         <v>46</v>
-      </c>
-      <c r="D520" t="s">
-        <v>47</v>
       </c>
       <c r="E520" t="s">
         <v>18</v>
@@ -17671,10 +17671,10 @@
         <v>2016</v>
       </c>
       <c r="C521" t="s">
+        <v>45</v>
+      </c>
+      <c r="D521" t="s">
         <v>46</v>
-      </c>
-      <c r="D521" t="s">
-        <v>47</v>
       </c>
       <c r="E521" t="s">
         <v>38</v>
@@ -17703,10 +17703,10 @@
         <v>2016</v>
       </c>
       <c r="C522" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D522" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E522" t="s">
         <v>21</v>
@@ -17735,10 +17735,10 @@
         <v>2016</v>
       </c>
       <c r="C523" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D523" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E523" t="s">
         <v>34</v>
@@ -17767,10 +17767,10 @@
         <v>2016</v>
       </c>
       <c r="C524" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D524" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E524" t="s">
         <v>40</v>
@@ -17799,10 +17799,10 @@
         <v>2016</v>
       </c>
       <c r="C525" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D525" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E525" t="s">
         <v>22</v>
@@ -17831,10 +17831,10 @@
         <v>2016</v>
       </c>
       <c r="C526" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D526" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E526" t="s">
         <v>18</v>
@@ -17863,10 +17863,10 @@
         <v>2016</v>
       </c>
       <c r="C527" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D527" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E527" t="s">
         <v>39</v>
@@ -17895,10 +17895,10 @@
         <v>2016</v>
       </c>
       <c r="C528" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D528" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E528" t="s">
         <v>42</v>
@@ -17927,10 +17927,10 @@
         <v>2016</v>
       </c>
       <c r="C529" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D529" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E529" t="s">
         <v>28</v>
@@ -17959,10 +17959,10 @@
         <v>2016</v>
       </c>
       <c r="C530" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D530" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E530" t="s">
         <v>21</v>
@@ -17991,10 +17991,10 @@
         <v>2016</v>
       </c>
       <c r="C531" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D531" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E531" t="s">
         <v>18</v>
@@ -18023,10 +18023,10 @@
         <v>2016</v>
       </c>
       <c r="C532" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D532" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E532" t="s">
         <v>40</v>
@@ -18055,10 +18055,10 @@
         <v>2016</v>
       </c>
       <c r="C533" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D533" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E533" t="s">
         <v>42</v>
@@ -18087,10 +18087,10 @@
         <v>2016</v>
       </c>
       <c r="C534" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D534" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E534" t="s">
         <v>40</v>
@@ -18099,7 +18099,7 @@
         <v>21</v>
       </c>
       <c r="G534" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H534">
         <v>34</v>
@@ -18119,10 +18119,10 @@
         <v>2016</v>
       </c>
       <c r="C535" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D535" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E535" t="s">
         <v>21</v>
@@ -18131,7 +18131,7 @@
         <v>40</v>
       </c>
       <c r="G535" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H535">
         <v>28</v>
